--- a/hira_material_automation/output/monthly/202601_202606__acl_primary_fixation_metal__040023__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__acl_primary_fixation_metal__040023__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-04T22:24:13</t>
+          <t>2026-06-14T22:17:31</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>5429f897f279dc227678016247d1277657dc8c1c401edb964bb993a5cd9a30c3</t>
+          <t>018f0b458f2fcf008e107e492e8e5ff5a99aaa016bea9e6a094ba4e5648afddd</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202606__acl_primary_fixation_metal__040023__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202606__acl_primary_fixation_metal__040023__normalized.xlsx
@@ -674,7 +674,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-14T22:17:31</t>
+          <t>2026-06-24T22:22:17</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>018f0b458f2fcf008e107e492e8e5ff5a99aaa016bea9e6a094ba4e5648afddd</t>
+          <t>c1112a640314ce95169bc4568ed945fc5066cb5bf4a801811c61d2237585f962</t>
         </is>
       </c>
     </row>
